--- a/ig/DM-SIDOBA/ValueSet-jdv-j404-qualification-orientation-ms.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-jdv-j404-qualification-orientation-ms.xlsx
@@ -117,7 +117,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r424-qualification-orientation</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r422-qualification-orientation</t>
   </si>
 </sst>
 </file>
